--- a/data/trans_orig/P36BPD14_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023</t>
+          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>45205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67936</t>
+          <t>68277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66729</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100725</t>
+          <t>101091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186917</t>
+          <t>185985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229215</t>
+          <t>231123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148823</t>
+          <t>148250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185088</t>
+          <t>183330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>344892</t>
+          <t>343451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>403406</t>
+          <t>400438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243049</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287749</t>
+          <t>289281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207599</t>
+          <t>208940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244472</t>
+          <t>244836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>460526</t>
+          <t>466167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>523340</t>
+          <t>526863</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50310</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>59223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>92035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173207</t>
+          <t>172460</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>215653</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125315</t>
+          <t>122817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156003</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308568</t>
+          <t>306609</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>362166</t>
+          <t>360146</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201022</t>
+          <t>202921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244265</t>
+          <t>245704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188456</t>
+          <t>187333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220803</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>397981</t>
+          <t>402373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>454329</t>
+          <t>458759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55319</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72269</t>
+          <t>71582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76514</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315532</t>
+          <t>318921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77235</t>
+          <t>76512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>111356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381061</t>
+          <t>377309</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302735</t>
+          <t>294868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>580624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>75266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96613</t>
+          <t>96435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388205</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708976</t>
+          <t>700421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97479</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>151036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93797</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132362</t>
+          <t>137964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228587</t>
+          <t>233603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386003</t>
+          <t>388697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454907</t>
+          <t>453336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160673</t>
+          <t>176522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393916</t>
+          <t>395381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>516348</t>
+          <t>506854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>823262</t>
+          <t>821903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>457083</t>
+          <t>456116</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>524072</t>
+          <t>525011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>495783</t>
+          <t>496185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>788135</t>
+          <t>762038</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>974521</t>
+          <t>975123</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1360715</t>
+          <t>1370808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37604</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69929</t>
+          <t>68018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>40538</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69162</t>
+          <t>69050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85308</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129368</t>
+          <t>128348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196514</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240760</t>
+          <t>242044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>274785</t>
+          <t>274068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>417053</t>
+          <t>422491</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481296</t>
+          <t>483562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>644692</t>
+          <t>642588</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180028</t>
+          <t>178666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223692</t>
+          <t>225322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>360910</t>
+          <t>355740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>524370</t>
+          <t>520270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>551651</t>
+          <t>557871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>740058</t>
+          <t>734353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76266</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110004</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86948</t>
+          <t>86574</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>131910</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93543</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144418</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371986</t>
+          <t>371442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>423017</t>
+          <t>423231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>479179</t>
+          <t>476806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>553419</t>
+          <t>552770</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>80561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>132104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>242517</t>
+          <t>241675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293548</t>
+          <t>292597</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>336137</t>
+          <t>334637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>406761</t>
+          <t>411216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>219231</t>
+          <t>215646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>327461</t>
+          <t>328712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>263107</t>
+          <t>262910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>364226</t>
+          <t>363834</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>525867</t>
+          <t>531019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>677968</t>
+          <t>673413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1068747</t>
+          <t>1015802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1483252</t>
+          <t>1483936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1194714</t>
+          <t>1155833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1572120</t>
+          <t>1558519</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2413727</t>
+          <t>2464021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2990443</t>
+          <t>3000030</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1581714</t>
+          <t>1575428</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2101162</t>
+          <t>2147269</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1645377</t>
+          <t>1662011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2112128</t>
+          <t>2141222</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3286773</t>
+          <t>3281932</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3969350</t>
+          <t>3933055</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD14_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>33623</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>48146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>59669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45205</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83256</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>73718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101091</t>
+          <t>110190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>207750</t>
+          <t>233590</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>185985</t>
+          <t>209006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231123</t>
+          <t>255976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>165646</t>
+          <t>186353</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148250</t>
+          <t>167862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183330</t>
+          <t>205288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>373396</t>
+          <t>419943</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343451</t>
+          <t>392843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>400438</t>
+          <t>454172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>267147</t>
+          <t>281594</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>245639</t>
+          <t>257756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289281</t>
+          <t>307205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>226969</t>
+          <t>242389</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208940</t>
+          <t>222876</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244836</t>
+          <t>260567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>494116</t>
+          <t>523983</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>466167</t>
+          <t>490348</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>526863</t>
+          <t>553332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>503301</t>
+          <t>548806</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503301</t>
+          <t>548806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>503301</t>
+          <t>548806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>950768</t>
+          <t>1037217</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>950768</t>
+          <t>1037217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>950768</t>
+          <t>1037217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>51970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>56800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>82479</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59223</t>
+          <t>67148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92035</t>
+          <t>100654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194016</t>
+          <t>210737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172460</t>
+          <t>187522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215653</t>
+          <t>233606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139118</t>
+          <t>156100</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122817</t>
+          <t>138259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156565</t>
+          <t>172657</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>333133</t>
+          <t>366838</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306609</t>
+          <t>339402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>360146</t>
+          <t>397516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>223505</t>
+          <t>234114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202921</t>
+          <t>211655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245704</t>
+          <t>258442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>204799</t>
+          <t>222925</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187333</t>
+          <t>205244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221719</t>
+          <t>242313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>428304</t>
+          <t>457038</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402373</t>
+          <t>429790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>458759</t>
+          <t>486750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57927</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71582</t>
+          <t>72323</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>194848</t>
+          <t>215084</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>193362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>318921</t>
+          <t>236546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66240</t>
+          <t>74800</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>86761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>261088</t>
+          <t>289884</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111356</t>
+          <t>266533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>377309</t>
+          <t>313785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>440290</t>
+          <t>218091</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294868</t>
+          <t>196118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580624</t>
+          <t>240259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86550</t>
+          <t>96055</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75266</t>
+          <t>82919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96435</t>
+          <t>107168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>526840</t>
+          <t>314146</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390835</t>
+          <t>289229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700421</t>
+          <t>337755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>121695</t>
+          <t>125168</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98293</t>
+          <t>102347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151036</t>
+          <t>151720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69168</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94682</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>190863</t>
+          <t>202084</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>177428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>233603</t>
+          <t>235014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>420940</t>
+          <t>455961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388697</t>
+          <t>421361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453336</t>
+          <t>492245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>303405</t>
+          <t>334917</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176522</t>
+          <t>311187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395381</t>
+          <t>359454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>724345</t>
+          <t>790879</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506854</t>
+          <t>744818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>821903</t>
+          <t>832874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>489913</t>
+          <t>548255</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>456116</t>
+          <t>515624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>525011</t>
+          <t>584644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>605521</t>
+          <t>449378</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>496185</t>
+          <t>422420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>762038</t>
+          <t>473658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1095433</t>
+          <t>997634</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>975123</t>
+          <t>958563</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1370808</t>
+          <t>1048235</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1032548</t>
+          <t>1129384</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1032548</t>
+          <t>1129384</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1032548</t>
+          <t>1129384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010641</t>
+          <t>1990596</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010641</t>
+          <t>1990596</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010641</t>
+          <t>1990596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>73947</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>54379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68018</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>66538</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>107006</t>
+          <t>140485</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84008</t>
+          <t>119739</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128348</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>218678</t>
+          <t>251630</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>228003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>242044</t>
+          <t>278102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>366423</t>
+          <t>371411</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>274068</t>
+          <t>347294</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>422491</t>
+          <t>395423</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>585101</t>
+          <t>623040</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>483562</t>
+          <t>586977</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>642588</t>
+          <t>658817</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>201910</t>
+          <t>237909</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178666</t>
+          <t>210935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225322</t>
+          <t>264622</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>411732</t>
+          <t>383858</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>355740</t>
+          <t>360581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>520270</t>
+          <t>408662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>613642</t>
+          <t>621767</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>557871</t>
+          <t>585312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>734353</t>
+          <t>654918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>472079</t>
+          <t>563486</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472079</t>
+          <t>563486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472079</t>
+          <t>563486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>833670</t>
+          <t>821806</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>833670</t>
+          <t>821806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>833670</t>
+          <t>821806</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1305749</t>
+          <t>1385292</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1305749</t>
+          <t>1385292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1305749</t>
+          <t>1385292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92411</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110186</t>
+          <t>125374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>106253</t>
+          <t>117145</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86574</t>
+          <t>96922</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>131910</t>
+          <t>142905</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>118793</t>
+          <t>128086</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91870</t>
+          <t>103253</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143540</t>
+          <t>149603</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>397481</t>
+          <t>443469</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371442</t>
+          <t>416399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>423231</t>
+          <t>472146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>516274</t>
+          <t>571556</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>476806</t>
+          <t>531964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>552770</t>
+          <t>607959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>105071</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80561</t>
+          <t>70675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132104</t>
+          <t>115795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>266245</t>
+          <t>291601</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241675</t>
+          <t>265466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>292597</t>
+          <t>316564</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>371316</t>
+          <t>384548</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>334637</t>
+          <t>347847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>411216</t>
+          <t>419800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>237706</t>
+          <t>234310</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>237706</t>
+          <t>234310</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>237706</t>
+          <t>234310</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>756137</t>
+          <t>838939</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>756137</t>
+          <t>838939</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>756137</t>
+          <t>838939</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>993843</t>
+          <t>1073249</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>993843</t>
+          <t>1073249</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>993843</t>
+          <t>1073249</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>282413</t>
+          <t>321948</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>215646</t>
+          <t>281803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>328712</t>
+          <t>364932</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>324730</t>
+          <t>367751</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>262910</t>
+          <t>336373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>363834</t>
+          <t>403367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>607143</t>
+          <t>689698</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>531019</t>
+          <t>640685</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>673413</t>
+          <t>743941</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1355025</t>
+          <t>1495087</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1015802</t>
+          <t>1434058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1483936</t>
+          <t>1562418</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1438312</t>
+          <t>1567050</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1155833</t>
+          <t>1511744</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1558519</t>
+          <t>1621094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2793337</t>
+          <t>3062138</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2464021</t>
+          <t>2971215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3000030</t>
+          <t>3138314</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1612909</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1575428</t>
+          <t>1548411</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2147269</t>
+          <t>1675498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1801816</t>
+          <t>1686206</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1662011</t>
+          <t>1636268</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2141222</t>
+          <t>1741442</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3529652</t>
+          <t>3299115</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3281932</t>
+          <t>3220037</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3933055</t>
+          <t>3397061</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3365273</t>
+          <t>3429944</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3365273</t>
+          <t>3429944</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3365273</t>
+          <t>3429944</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3564858</t>
+          <t>3621007</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3564858</t>
+          <t>3621007</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3564858</t>
+          <t>3621007</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6930132</t>
+          <t>7050951</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6930132</t>
+          <t>7050951</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6930132</t>
+          <t>7050951</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
